--- a/hospital_traversing_robot/BOM.xlsx
+++ b/hospital_traversing_robot/BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">DIP28 socket</t>
   </si>
   <si>
-    <t xml:space="preserve">LM317</t>
+    <t xml:space="preserve">LD33v</t>
   </si>
   <si>
     <t xml:space="preserve">L7805</t>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Resistors</t>
   </si>
   <si>
-    <t xml:space="preserve">Pin Headers Female</t>
+    <t xml:space="preserve">Pin Headers Female 1x40</t>
   </si>
   <si>
     <t xml:space="preserve">Pin Header Female 1x3</t>
@@ -79,10 +79,7 @@
     <t xml:space="preserve">nRF24l01</t>
   </si>
   <si>
-    <t xml:space="preserve">ALREADY BOUGHT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pin Header 2x3</t>
+    <t xml:space="preserve">Pin Header Female 2x3</t>
   </si>
   <si>
     <t xml:space="preserve">MPU9250</t>
@@ -127,10 +124,13 @@
     <t xml:space="preserve">18650 Li-ION</t>
   </si>
   <si>
-    <t xml:space="preserve">Battery Holder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RC Frame with DC Motors</t>
+    <t xml:space="preserve">BMS 2s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nickel Strips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geared 5v DC Motors</t>
   </si>
   <si>
     <t xml:space="preserve">Nylon Spacers 12mm</t>
@@ -162,7 +162,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -186,16 +186,23 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFEEEEEE"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFEEEEEE"/>
       <name val="Aptos Narrow"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFEEEEEE"/>
       <name val="Aptos Narrow"/>
       <family val="0"/>
       <charset val="1"/>
@@ -210,8 +217,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF666666"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
   </fills>
@@ -382,108 +389,116 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -496,6 +511,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFEEEEEE"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666666"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -504,725 +579,721 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="8" style="1" width="10.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="7" t="n">
         <v>140</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7" t="n">
+      <c r="D2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <f aca="false">C2*D2</f>
         <v>140</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="D3" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12" t="n">
+      <c r="D3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13" t="n">
         <f aca="false">C3*D3</f>
         <v>100</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="12"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12" t="n">
+      <c r="D4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="13" t="n">
         <f aca="false">C4*D4</f>
         <v>3</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="12"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <f aca="false">C5*D5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="14"/>
+      <c r="G5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <f aca="false">C5*D5</f>
-        <v>15</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="12"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12" t="n">
+      <c r="D6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="13" t="n">
         <f aca="false">C6*D6</f>
         <v>15</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="12"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="12" t="n">
+      <c r="D7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13" t="n">
         <f aca="false">C7*D7</f>
         <v>4</v>
       </c>
-      <c r="G7" s="12"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="12" t="n">
+      <c r="D8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13" t="n">
         <f aca="false">C8*D8</f>
         <v>15</v>
       </c>
-      <c r="G8" s="12"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="C9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <f aca="false">C9*D9</f>
-        <v>4</v>
-      </c>
-      <c r="G9" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="12" t="n">
+      <c r="D10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13" t="n">
         <f aca="false">C10*D10</f>
         <v>5</v>
       </c>
-      <c r="G10" s="12"/>
+      <c r="G10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12" t="n">
+      <c r="D11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13" t="n">
         <f aca="false">C11*D11</f>
         <v>3</v>
       </c>
-      <c r="G11" s="12"/>
+      <c r="G11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>680</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="12" t="n">
+      <c r="D12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13" t="n">
         <f aca="false">C12*D12</f>
         <v>680</v>
       </c>
-      <c r="G12" s="12"/>
+      <c r="G12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12" t="n">
+      <c r="D13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="13" t="n">
         <f aca="false">C13*D13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="12" t="n">
+      <c r="D14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13" t="n">
         <f aca="false">C14*D14</f>
         <v>6</v>
       </c>
-      <c r="G14" s="12"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="11" t="n">
+      <c r="B15" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="12" t="n">
         <v>475</v>
       </c>
-      <c r="D15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="12" t="n">
+      <c r="D15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13" t="n">
         <f aca="false">C15*D15</f>
         <v>475</v>
       </c>
-      <c r="G15" s="12"/>
+      <c r="G15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="11" t="n">
+      <c r="B16" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="12" t="n">
+      <c r="D16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13" t="n">
         <f aca="false">C16*D16</f>
         <v>2</v>
       </c>
-      <c r="G16" s="12"/>
+      <c r="G16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="11" t="n">
+      <c r="B17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <f aca="false">C17*D17</f>
         <v>14</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="D18" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="12" t="n">
+      <c r="D18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="13" t="n">
         <f aca="false">C18*D18</f>
         <v>45</v>
       </c>
-      <c r="G18" s="12"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="11" t="n">
+      <c r="B19" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="12" t="n">
+      <c r="D19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="13" t="n">
         <f aca="false">C19*D19</f>
         <v>5</v>
       </c>
-      <c r="G19" s="12"/>
+      <c r="G19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="11" t="n">
+      <c r="B20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="D20" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="12" t="n">
+      <c r="D20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13" t="n">
         <f aca="false">C20*D20</f>
         <v>12</v>
       </c>
-      <c r="G20" s="12"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="11" t="n">
+      <c r="B21" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12" t="n">
+      <c r="D21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="13" t="n">
         <f aca="false">C21*D21</f>
         <v>6</v>
       </c>
-      <c r="G21" s="12"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <f aca="false">C22*D22</f>
+        <v>1</v>
+      </c>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <f aca="false">C22*D22</f>
-        <v>1</v>
-      </c>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12" t="n">
+      <c r="D23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="13" t="n">
         <f aca="false">C23*D23</f>
         <v>0</v>
       </c>
-      <c r="F23" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="12"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="11" t="n">
+      <c r="B24" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="13" t="n">
         <f aca="false">C24*D24</f>
         <v>6</v>
       </c>
-      <c r="G24" s="12"/>
+      <c r="G24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="11" t="n">
+      <c r="B25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="13" t="n">
         <f aca="false">C25*D25</f>
         <v>16</v>
       </c>
-      <c r="G25" s="12"/>
+      <c r="G25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="11" t="n">
+      <c r="B26" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="13" t="n">
         <f aca="false">C26*D26</f>
         <v>25</v>
       </c>
-      <c r="G26" s="12"/>
+      <c r="G26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="11" t="n">
+      <c r="B27" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="13" t="n">
         <f aca="false">C27*D27</f>
         <v>0</v>
       </c>
-      <c r="F27" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="12"/>
+      <c r="G27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="11" t="n">
+      <c r="B28" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="12" t="n">
+      <c r="D28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13" t="n">
         <f aca="false">C28*D28</f>
         <v>0</v>
       </c>
-      <c r="F28" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" s="12"/>
+      <c r="G28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="13"/>
+      <c r="G29" s="13"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C30" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <f aca="false">C29*D29</f>
+      <c r="D30" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <f aca="false">C30*D30</f>
         <v>0</v>
       </c>
-      <c r="F29" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="10" t="s">
+      <c r="G30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C31" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D31" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="12" t="n">
-        <f aca="false">C30*D30</f>
+      <c r="E31" s="13" t="n">
+        <f aca="false">C31*D31</f>
         <v>30</v>
       </c>
-      <c r="G30" s="12"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="10" t="s">
+      <c r="G31" s="13"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C32" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="12" t="n">
-        <f aca="false">C31*D31</f>
+      <c r="E32" s="13" t="n">
+        <f aca="false">C32*D32</f>
         <v>24</v>
       </c>
-      <c r="G31" s="12"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="10" t="s">
+      <c r="G32" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D33" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="12" t="n">
-        <f aca="false">C32*D32</f>
+      <c r="E33" s="13" t="n">
+        <f aca="false">C33*D33</f>
         <v>12</v>
       </c>
-      <c r="G32" s="12"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12"/>
-      <c r="G33" s="12"/>
+      <c r="G33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="13"/>
+      <c r="G34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B35" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="C35" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="12" t="n">
-        <f aca="false">C34*D34</f>
+      <c r="E35" s="13" t="n">
+        <f aca="false">C35*D35</f>
         <v>140</v>
       </c>
-      <c r="F34" s="13"/>
-      <c r="G34" s="14"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15"/>
-      <c r="B36" s="16" t="s">
+      <c r="A36" s="5"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16"/>
+      <c r="B37" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F36" s="13"/>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1"/>
-      <c r="B38" s="22" t="s">
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="13"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="24" t="n">
-        <f aca="false">SUM(E2:E37)</f>
-        <v>3803</v>
-      </c>
-      <c r="F38" s="25"/>
-      <c r="G38" s="21"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="26" t="n">
+        <f aca="false">SUM(E2:E38)</f>
+        <v>1792</v>
+      </c>
+      <c r="F39" s="27"/>
+      <c r="G39" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/hospital_traversing_robot/BOM.xlsx
+++ b/hospital_traversing_robot/BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -152,6 +152,12 @@
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approx </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given </t>
   </si>
 </sst>
 </file>
@@ -579,7 +585,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -682,13 +688,15 @@
       <c r="B5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="12"/>
+      <c r="C5" s="12" t="n">
+        <v>20</v>
+      </c>
       <c r="D5" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="13" t="n">
         <f aca="false">C5*D5</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="13"/>
@@ -835,14 +843,14 @@
         <v>18</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="13" t="n">
         <f aca="false">C13*D13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G13" s="13"/>
     </row>
@@ -1028,14 +1036,14 @@
         <v>29</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="13" t="n">
         <f aca="false">C23*D23</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G23" s="13"/>
     </row>
@@ -1104,14 +1112,14 @@
         <v>33</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D27" s="12" t="n">
         <v>2</v>
       </c>
       <c r="E27" s="13" t="n">
         <f aca="false">C27*D27</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G27" s="13"/>
     </row>
@@ -1123,14 +1131,14 @@
         <v>34</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="13" t="n">
         <f aca="false">C28*D28</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G28" s="13"/>
     </row>
@@ -1141,11 +1149,16 @@
       <c r="B29" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="12"/>
+      <c r="C29" s="12" t="n">
+        <v>10</v>
+      </c>
       <c r="D29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="13"/>
+      <c r="E29" s="13" t="n">
+        <f aca="false">C29*D29</f>
+        <v>10</v>
+      </c>
       <c r="G29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1156,14 +1169,14 @@
         <v>36</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="E30" s="13" t="n">
         <f aca="false">C30*D30</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G30" s="13"/>
     </row>
@@ -1240,14 +1253,14 @@
         <v>41</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E35" s="13" t="n">
         <f aca="false">C35*D35</f>
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="F35" s="14"/>
       <c r="G35" s="15"/>
@@ -1290,10 +1303,26 @@
       <c r="D39" s="25"/>
       <c r="E39" s="26" t="n">
         <f aca="false">SUM(E2:E38)</f>
-        <v>1792</v>
+        <v>2592</v>
       </c>
       <c r="F39" s="27"/>
       <c r="G39" s="23"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>5000</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
